--- a/backend/records/AttendanceRecords.xlsx
+++ b/backend/records/AttendanceRecords.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Student Name</t>
   </si>
@@ -37,16 +37,7 @@
     <t>Present</t>
   </si>
   <si>
-    <t>7/8/2025, 10:51:02 am</t>
-  </si>
-  <si>
-    <t>mummy</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>7/8/2025, 6:50:34 pm</t>
+    <t>7/8/2025, 7:19:42 pm</t>
   </si>
 </sst>
 </file>
@@ -423,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -464,20 +455,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/backend/records/AttendanceRecords.xlsx
+++ b/backend/records/AttendanceRecords.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Student Name</t>
   </si>
@@ -28,25 +28,31 @@
     <t>Image</t>
   </si>
   <si>
-    <t>prashant</t>
-  </si>
-  <si>
-    <t>202303103510015</t>
+    <t>het</t>
+  </si>
+  <si>
+    <t>101</t>
   </si>
   <si>
     <t>Present</t>
   </si>
   <si>
-    <t>7/8/2025, 10:51:02 am</t>
-  </si>
-  <si>
-    <t>mummy</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>7/8/2025, 6:50:34 pm</t>
+    <t>7/8/2025, 10:49:35 am</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>7/8/2025, 7:26:21 pm</t>
+  </si>
+  <si>
+    <t>rr</t>
+  </si>
+  <si>
+    <t>12334</t>
+  </si>
+  <si>
+    <t>7/8/2025, 7:45:17 pm</t>
   </si>
 </sst>
 </file>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -466,16 +472,30 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/backend/records/AttendanceRecords.xlsx
+++ b/backend/records/AttendanceRecords.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Student Name</t>
   </si>
@@ -28,31 +28,16 @@
     <t>Image</t>
   </si>
   <si>
-    <t>het</t>
-  </si>
-  <si>
-    <t>101</t>
+    <t>prashant</t>
+  </si>
+  <si>
+    <t>202303103510015</t>
   </si>
   <si>
     <t>Present</t>
   </si>
   <si>
-    <t>7/8/2025, 10:49:35 am</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>7/8/2025, 7:26:21 pm</t>
-  </si>
-  <si>
-    <t>rr</t>
-  </si>
-  <si>
-    <t>12334</t>
-  </si>
-  <si>
-    <t>7/8/2025, 7:45:17 pm</t>
+    <t>8/8/2025, 10:15:10 am</t>
   </si>
 </sst>
 </file>
@@ -429,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -470,34 +455,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/backend/records/AttendanceRecords.xlsx
+++ b/backend/records/AttendanceRecords.xlsx
@@ -31,28 +31,28 @@
     <t>het</t>
   </si>
   <si>
+    <t>2023031035100</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>7/2/2026, 5:05:42 PM</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>7/8/2025, 10:49:35 am</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>7/8/2025, 7:26:21 pm</t>
-  </si>
-  <si>
-    <t>rr</t>
-  </si>
-  <si>
-    <t>12334</t>
-  </si>
-  <si>
-    <t>7/8/2025, 7:45:17 pm</t>
+    <t>7/2/2026, 5:07:31 PM</t>
+  </si>
+  <si>
+    <t>darshan</t>
+  </si>
+  <si>
+    <t>202303103510002</t>
+  </si>
+  <si>
+    <t>7/2/2026, 5:07:54 PM</t>
   </si>
 </sst>
 </file>
